--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.42.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.42.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.42.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.42.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.42.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.42.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0042.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0042.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: when, where and how, such Subp Ã¦ na was served, and by</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to prejudice the Plaintiffâ€™s right to be allowed the costs</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]35</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]35</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: symbol-only separator/garbage line :: 1850.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: a</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]35</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,11 +666,7 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: dence that any Defendant, against whom a Subp Ã¦ na to</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: -</t>
+          <t>L89: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -713,11 +713,7 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: more than two years before the Subp Ã¦ ena was issued, and</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -726,7 +722,11 @@
           <t>L52: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L91: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -760,11 +760,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -813,7 +809,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -953,7 +949,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -997,7 +993,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1036,7 +1032,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
